--- a/Asgari-ucret.xlsx
+++ b/Asgari-ucret.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0669CD27-C329-4629-BAE4-B88847E8118D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F565302B-23EE-4C3C-93B9-144B25259ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -370,8 +370,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd/mmm"/>
     <numFmt numFmtId="165" formatCode="%0"/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="173" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="167" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -548,17 +548,17 @@
     <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1096,10 +1096,10 @@
       </c>
       <c r="C6" s="17">
         <f>$B$6*D6</f>
-        <v>340</v>
+        <v>612</v>
       </c>
       <c r="D6" s="18">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E6" s="17">
         <f>$B$6*F6</f>
@@ -1110,28 +1110,28 @@
       </c>
       <c r="G6" s="1">
         <f>D6/F6</f>
-        <v>0.83333333333333337</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="17">
         <f>$B$6*I6</f>
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="I6" s="20">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J6" s="17">
         <f>$B$6*K6</f>
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="K6" s="21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L6" s="17">
         <f>$B$6*M6</f>
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="M6" s="22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N6" s="17">
         <f>$B$6*O6</f>
@@ -1142,33 +1142,33 @@
       </c>
       <c r="P6" s="17">
         <f>$B$6*Q6</f>
-        <v>340</v>
+        <v>408</v>
       </c>
       <c r="Q6" s="24">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R6" s="17">
         <f>$B$6*S6</f>
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="S6" s="25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" s="17">
         <f>$B$6*U6</f>
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="U6" s="25">
         <f>S6</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V6" s="17">
         <f>$B$6*W6</f>
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="W6" s="25">
         <f>S6</f>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="Q14" s="3">
         <f>L6+N6+P6+R6+T6+V6</f>
-        <v>1292</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Q15" s="28">
         <f>C6</f>
-        <v>340</v>
+        <v>612</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="Q17" s="16">
         <f>+H6+J6</f>
-        <v>289</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Q19" s="3">
         <f>SUM(Q14:Q18)</f>
-        <v>2329</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1804,7 +1804,7 @@
   <sheetData>
     <row r="4" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="31"/>
-      <c r="C4" s="45"/>
+      <c r="C4" s="51"/>
       <c r="D4" s="32"/>
       <c r="E4" s="29">
         <f>E9/E16</f>
@@ -1819,7 +1819,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="31"/>
-      <c r="C5" s="45"/>
+      <c r="C5" s="51"/>
       <c r="D5" s="32"/>
       <c r="E5" s="33"/>
       <c r="F5" s="33"/>
@@ -1829,7 +1829,7 @@
       <c r="B6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="51" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="32"/>
@@ -1856,7 +1856,7 @@
       <c r="B7" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="45"/>
+      <c r="C7" s="51"/>
       <c r="D7" s="32"/>
       <c r="E7" s="33" t="s">
         <v>37</v>
@@ -1876,7 +1876,7 @@
       <c r="F8" s="33"/>
       <c r="G8" s="33"/>
       <c r="M8" s="29">
-        <f>M9+(M9*D9)</f>
+        <f t="shared" ref="M8:M14" si="0">M9+(M9*D9)</f>
         <v>12707.133110481325</v>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       <c r="C9" s="32">
         <v>2024</v>
       </c>
-      <c r="D9" s="49">
+      <c r="D9" s="48">
         <v>0.49109999999999998</v>
       </c>
       <c r="E9" s="33">
@@ -1901,12 +1901,12 @@
       <c r="J9" s="29">
         <v>10416.25</v>
       </c>
-      <c r="K9" s="50">
-        <f>I9-D9</f>
+      <c r="K9" s="49">
+        <f t="shared" ref="K9:K16" si="1">I9-D9</f>
         <v>-0.49109999999999998</v>
       </c>
       <c r="M9" s="29">
-        <f>M10+(M10*D10)</f>
+        <f t="shared" si="0"/>
         <v>8521.9858564022034</v>
       </c>
     </row>
@@ -1917,8 +1917,8 @@
       <c r="C10" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="49">
-        <f>1-(E10/E9)</f>
+      <c r="D10" s="48">
+        <f t="shared" ref="D10:D19" si="2">1-(E10/E9)</f>
         <v>0.32935419362427953</v>
       </c>
       <c r="E10" s="35">
@@ -1930,20 +1930,20 @@
       <c r="G10" s="35">
         <v>15762.04</v>
       </c>
-      <c r="I10" s="49">
-        <f>(J9/J10)-1</f>
+      <c r="I10" s="48">
+        <f t="shared" ref="I10:I16" si="3">(J9/J10)-1</f>
         <v>0.38883333333333336</v>
       </c>
       <c r="J10" s="30">
         <f>Sayfa3!C15</f>
         <v>7500</v>
       </c>
-      <c r="K10" s="50">
-        <f>I10-D10</f>
+      <c r="K10" s="49">
+        <f t="shared" si="1"/>
         <v>5.947913970905383E-2</v>
       </c>
       <c r="M10" s="29">
-        <f>M11+(M11*D11)</f>
+        <f t="shared" si="0"/>
         <v>6410.6209596167309</v>
       </c>
     </row>
@@ -1954,8 +1954,8 @@
       <c r="C11" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="49">
-        <f>1-(E11/E10)</f>
+      <c r="D11" s="48">
+        <f t="shared" si="2"/>
         <v>0.25394130317338937</v>
       </c>
       <c r="E11" s="35">
@@ -1967,20 +1967,20 @@
       <c r="G11" s="35">
         <v>11759.4</v>
       </c>
-      <c r="I11" s="49">
-        <f>(J10/J11)-1</f>
+      <c r="I11" s="48">
+        <f t="shared" si="3"/>
         <v>0.35154616881712686</v>
       </c>
       <c r="J11" s="30">
         <f>Sayfa3!C22</f>
         <v>5549.2</v>
       </c>
-      <c r="K11" s="50">
-        <f>I11-D11</f>
+      <c r="K11" s="49">
+        <f t="shared" si="1"/>
         <v>9.7604865643737493E-2</v>
       </c>
       <c r="M11" s="29">
-        <f>M12+(M12*D12)</f>
+        <f t="shared" si="0"/>
         <v>5112.3772248295572</v>
       </c>
     </row>
@@ -1991,8 +1991,8 @@
       <c r="C12" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="49">
-        <f>1-(E12/E11)</f>
+      <c r="D12" s="48">
+        <f t="shared" si="2"/>
         <v>0.35341726618705027</v>
       </c>
       <c r="E12" s="35">
@@ -2004,20 +2004,20 @@
       <c r="G12" s="35">
         <v>7603.43</v>
       </c>
-      <c r="I12" s="49">
-        <f>(J11/J12)-1</f>
+      <c r="I12" s="48">
+        <f t="shared" si="3"/>
         <v>0.29066170484940113</v>
       </c>
       <c r="J12" s="30">
         <f>Sayfa3!C25</f>
         <v>4299.5</v>
       </c>
-      <c r="K12" s="50">
-        <f>I12-D12</f>
+      <c r="K12" s="49">
+        <f t="shared" si="1"/>
         <v>-6.2755561337649146E-2</v>
       </c>
       <c r="M12" s="29">
-        <f>M13+(M13*D13)</f>
+        <f t="shared" si="0"/>
         <v>3777.3843681132676</v>
       </c>
     </row>
@@ -2028,8 +2028,8 @@
       <c r="C13" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="49">
-        <f>1-(E13/E12)</f>
+      <c r="D13" s="48">
+        <f t="shared" si="2"/>
         <v>0.22670375521557729</v>
       </c>
       <c r="E13" s="35">
@@ -2041,20 +2041,20 @@
       <c r="G13" s="35">
         <v>5879.7</v>
       </c>
-      <c r="I13" s="49">
-        <f>(J12/J13)-1</f>
+      <c r="I13" s="48">
+        <f t="shared" si="3"/>
         <v>0.42350109423679894</v>
       </c>
       <c r="J13" s="30">
         <f>Sayfa3!C29</f>
         <v>3020.37</v>
       </c>
-      <c r="K13" s="50">
-        <f>I13-D13</f>
+      <c r="K13" s="49">
+        <f t="shared" si="1"/>
         <v>0.19679733902122165</v>
       </c>
       <c r="M13" s="29">
-        <f>M14+(M14*D14)</f>
+        <f t="shared" si="0"/>
         <v>3079.2963272941488</v>
       </c>
     </row>
@@ -2065,8 +2065,8 @@
       <c r="C14" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="49">
-        <f>1-(E14/E13)</f>
+      <c r="D14" s="48">
+        <f t="shared" si="2"/>
         <v>0.33561386185169506</v>
       </c>
       <c r="E14" s="35">
@@ -2078,20 +2078,20 @@
       <c r="G14" s="35">
         <v>4203.5600000000004</v>
       </c>
-      <c r="I14" s="49">
-        <f>(J13/J14)-1</f>
+      <c r="I14" s="48">
+        <f t="shared" si="3"/>
         <v>0.25469726866756659</v>
       </c>
       <c r="J14" s="30">
         <f>Sayfa3!C31</f>
         <v>2407.25</v>
       </c>
-      <c r="K14" s="50">
-        <f>I14-D14</f>
+      <c r="K14" s="49">
+        <f t="shared" si="1"/>
         <v>-8.0916593184128471E-2</v>
       </c>
       <c r="M14" s="29">
-        <f>M15+(M15*D15)</f>
+        <f t="shared" si="0"/>
         <v>2305.5288772048325</v>
       </c>
     </row>
@@ -2102,8 +2102,8 @@
       <c r="C15" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="49">
-        <f>1-(E15/E14)</f>
+      <c r="D15" s="48">
+        <f t="shared" si="2"/>
         <v>0.17735588662019186</v>
       </c>
       <c r="E15" s="35">
@@ -2115,16 +2115,16 @@
       <c r="G15" s="35">
         <v>3458.03</v>
       </c>
-      <c r="I15" s="49">
-        <f>(J14/J15)-1</f>
+      <c r="I15" s="48">
+        <f t="shared" si="3"/>
         <v>0.24284932468712572</v>
       </c>
       <c r="J15" s="30">
         <f>Sayfa3!C41</f>
         <v>1936.88</v>
       </c>
-      <c r="K15" s="50">
-        <f>I15-D15</f>
+      <c r="K15" s="49">
+        <f t="shared" si="1"/>
         <v>6.5493438066933862E-2</v>
       </c>
       <c r="M15" s="29">
@@ -2139,8 +2139,8 @@
       <c r="C16" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="49">
-        <f>1-(E16/E15)</f>
+      <c r="D16" s="48">
+        <f t="shared" si="2"/>
         <v>0.13068726851951429</v>
       </c>
       <c r="E16" s="35">
@@ -2152,16 +2152,16 @@
       <c r="G16" s="35">
         <v>3006.12</v>
       </c>
-      <c r="I16" s="49">
-        <f>(J15/J16)-1</f>
+      <c r="I16" s="48">
+        <f t="shared" si="3"/>
         <v>0.11836202068260682</v>
       </c>
       <c r="J16" s="30">
         <f>Sayfa3!C48</f>
         <v>1731.89</v>
       </c>
-      <c r="K16" s="50">
-        <f>I16-D16</f>
+      <c r="K16" s="49">
+        <f t="shared" si="1"/>
         <v>-1.2325247836907471E-2</v>
       </c>
     </row>
@@ -2172,8 +2172,8 @@
       <c r="C17" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="49">
-        <f>1-(E17/E16)</f>
+      <c r="D17" s="48">
+        <f t="shared" si="2"/>
         <v>0.20672967489732308</v>
       </c>
       <c r="E17" s="35">
@@ -2193,8 +2193,8 @@
       <c r="C18" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="49">
-        <f>1-(E18/E17)</f>
+      <c r="D18" s="48">
+        <f t="shared" si="2"/>
         <v>0.12417036778282342</v>
       </c>
       <c r="E18" s="35">
@@ -2214,8 +2214,8 @@
       <c r="C19" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="49">
-        <f>1-(E19/E18)</f>
+      <c r="D19" s="48">
+        <f t="shared" si="2"/>
         <v>7.3408543794424741E-2</v>
       </c>
       <c r="E19" s="35">
@@ -2256,11 +2256,11 @@
       <c r="C23" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="51"/>
+      <c r="E23" s="50"/>
       <c r="F23" s="30">
         <v>1071</v>
       </c>
-      <c r="J23" s="51"/>
+      <c r="J23" s="50"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C24" s="29" t="s">
@@ -2527,419 +2527,419 @@
   <cols>
     <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.28515625" style="26" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="47" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B1" s="46"/>
+      <c r="B1" s="45"/>
       <c r="C1" s="30"/>
-      <c r="D1" s="47"/>
+      <c r="D1" s="46"/>
     </row>
     <row r="2" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B2" s="46"/>
+      <c r="B2" s="45"/>
       <c r="C2" s="30"/>
-      <c r="D2" s="47"/>
+      <c r="D2" s="46"/>
     </row>
     <row r="3" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B3" s="46"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="30"/>
-      <c r="D3" s="47"/>
+      <c r="D3" s="46"/>
     </row>
     <row r="4" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B4" s="46"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="30"/>
-      <c r="D4" s="47"/>
+      <c r="D4" s="46"/>
     </row>
     <row r="5" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B5" s="46"/>
+      <c r="B5" s="45"/>
       <c r="C5" s="30"/>
-      <c r="D5" s="47"/>
+      <c r="D5" s="46"/>
     </row>
     <row r="6" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B6" s="46"/>
+      <c r="B6" s="45"/>
       <c r="C6" s="30"/>
-      <c r="D6" s="47"/>
+      <c r="D6" s="46"/>
     </row>
     <row r="7" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B7" s="46"/>
+      <c r="B7" s="45"/>
       <c r="C7" s="30"/>
-      <c r="D7" s="47"/>
+      <c r="D7" s="46"/>
     </row>
     <row r="8" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B8" s="46"/>
+      <c r="B8" s="45"/>
       <c r="C8" s="30"/>
-      <c r="D8" s="47"/>
+      <c r="D8" s="46"/>
     </row>
     <row r="9" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B9" s="46"/>
+      <c r="B9" s="45"/>
       <c r="C9" s="30"/>
-      <c r="D9" s="47"/>
+      <c r="D9" s="46"/>
     </row>
     <row r="10" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B10" s="46"/>
+      <c r="B10" s="45"/>
       <c r="C10" s="30"/>
-      <c r="D10" s="47"/>
+      <c r="D10" s="46"/>
     </row>
     <row r="11" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B11" s="46">
+      <c r="B11" s="45">
         <v>45318</v>
       </c>
       <c r="C11" s="30">
         <v>10000</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B12" s="46"/>
+      <c r="B12" s="45"/>
       <c r="C12" s="30"/>
-      <c r="D12" s="47"/>
+      <c r="D12" s="46"/>
     </row>
     <row r="13" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B13" s="46">
+      <c r="B13" s="45">
         <v>45287</v>
       </c>
       <c r="C13" s="30">
         <v>7432.53</v>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B14" s="46">
+      <c r="B14" s="45">
         <v>45244</v>
       </c>
       <c r="C14" s="30">
         <v>5000</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B15" s="46">
+      <c r="B15" s="45">
         <v>45134</v>
       </c>
       <c r="C15" s="30">
         <v>7500</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="46">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B16" s="46"/>
+      <c r="B16" s="45"/>
       <c r="C16" s="30"/>
-      <c r="D16" s="47"/>
+      <c r="D16" s="46"/>
     </row>
     <row r="17" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B17" s="46">
+      <c r="B17" s="45">
         <v>45099</v>
       </c>
       <c r="C17" s="30">
         <v>2000</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B18" s="46">
+      <c r="B18" s="45">
         <v>45034</v>
       </c>
       <c r="C18" s="30">
         <v>7500</v>
       </c>
-      <c r="D18" s="47">
+      <c r="D18" s="46">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B19" s="46">
+      <c r="B19" s="45">
         <v>45034</v>
       </c>
       <c r="C19" s="30">
         <v>2000</v>
       </c>
-      <c r="D19" s="47">
+      <c r="D19" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B20" s="46">
+      <c r="B20" s="45">
         <v>45012</v>
       </c>
       <c r="C20" s="30">
         <v>5589.34</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B21" s="46">
+      <c r="B21" s="45">
         <v>44974</v>
       </c>
       <c r="C21" s="30">
         <v>5570.01</v>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B22" s="46">
+      <c r="B22" s="45">
         <v>44953</v>
       </c>
       <c r="C22" s="30">
         <v>5549.2</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B23" s="46"/>
+      <c r="B23" s="45"/>
       <c r="C23" s="30"/>
-      <c r="D23" s="47"/>
+      <c r="D23" s="46"/>
     </row>
     <row r="24" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B24" s="46">
+      <c r="B24" s="45">
         <v>44861</v>
       </c>
       <c r="C24" s="30">
         <v>4293.6499999999996</v>
       </c>
-      <c r="D24" s="47">
+      <c r="D24" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B25" s="46">
+      <c r="B25" s="45">
         <v>44769</v>
       </c>
       <c r="C25" s="30">
         <v>4299.5</v>
       </c>
-      <c r="D25" s="47">
+      <c r="D25" s="46">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B26" s="46">
+      <c r="B26" s="45">
         <v>44749</v>
       </c>
       <c r="C26" s="30">
         <v>1100</v>
       </c>
-      <c r="D26" s="47">
+      <c r="D26" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B27" s="46"/>
+      <c r="B27" s="45"/>
       <c r="C27" s="30"/>
-      <c r="D27" s="47"/>
+      <c r="D27" s="46"/>
     </row>
     <row r="28" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B28" s="46">
+      <c r="B28" s="45">
         <v>44680</v>
       </c>
       <c r="C28" s="30">
         <v>1100</v>
       </c>
-      <c r="D28" s="47">
+      <c r="D28" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B29" s="46">
+      <c r="B29" s="45">
         <v>44588</v>
       </c>
       <c r="C29" s="30">
         <v>3020.37</v>
       </c>
-      <c r="D29" s="47">
+      <c r="D29" s="46">
         <v>6</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B30" s="46"/>
+      <c r="B30" s="45"/>
       <c r="C30" s="30"/>
-      <c r="D30" s="47"/>
+      <c r="D30" s="46"/>
     </row>
     <row r="31" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B31" s="46">
+      <c r="B31" s="45">
         <v>44557</v>
       </c>
       <c r="C31" s="30">
         <v>2407.25</v>
       </c>
-      <c r="D31" s="47">
+      <c r="D31" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="46"/>
+      <c r="B32" s="45"/>
       <c r="C32" s="30"/>
-      <c r="D32" s="47"/>
+      <c r="D32" s="46"/>
     </row>
     <row r="33" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B33" s="46"/>
+      <c r="B33" s="45"/>
       <c r="C33" s="30"/>
-      <c r="D33" s="47"/>
+      <c r="D33" s="46"/>
     </row>
     <row r="34" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B34" s="46"/>
+      <c r="B34" s="45"/>
       <c r="C34" s="30"/>
-      <c r="D34" s="47"/>
+      <c r="D34" s="46"/>
     </row>
     <row r="35" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B35" s="46">
+      <c r="B35" s="45">
         <v>44039</v>
       </c>
       <c r="C35" s="30">
         <v>2048.25</v>
       </c>
-      <c r="D35" s="47">
+      <c r="D35" s="46">
         <v>6</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B36" s="46">
+      <c r="B36" s="45">
         <v>44039</v>
       </c>
       <c r="C36" s="30">
         <v>1000</v>
       </c>
-      <c r="D36" s="47">
+      <c r="D36" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B37" s="46"/>
+      <c r="B37" s="45"/>
       <c r="C37" s="30"/>
-      <c r="D37" s="47"/>
+      <c r="D37" s="46"/>
     </row>
     <row r="38" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B38" s="46">
+      <c r="B38" s="45">
         <v>44008</v>
       </c>
       <c r="C38" s="30">
         <v>1907.58</v>
       </c>
-      <c r="D38" s="47">
+      <c r="D38" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B39" s="46">
+      <c r="B39" s="45">
         <v>43972</v>
       </c>
       <c r="C39" s="30">
         <v>1909.32</v>
       </c>
-      <c r="D39" s="47">
+      <c r="D39" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B40" s="46">
+      <c r="B40" s="45">
         <v>43932</v>
       </c>
       <c r="C40" s="30">
         <v>1000</v>
       </c>
-      <c r="D40" s="47">
+      <c r="D40" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B41" s="46">
+      <c r="B41" s="45">
         <v>43857</v>
       </c>
       <c r="C41" s="30">
         <v>1936.88</v>
       </c>
-      <c r="D41" s="47">
+      <c r="D41" s="46">
         <v>4</v>
       </c>
     </row>
     <row r="42" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B42" s="46"/>
+      <c r="B42" s="45"/>
       <c r="C42" s="30"/>
-      <c r="D42" s="47"/>
+      <c r="D42" s="46"/>
     </row>
     <row r="43" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B43" s="46">
+      <c r="B43" s="45">
         <v>43704</v>
       </c>
       <c r="C43" s="30">
         <v>1790.78</v>
       </c>
-      <c r="D43" s="47">
+      <c r="D43" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B44" s="46">
+      <c r="B44" s="45">
         <v>43686</v>
       </c>
       <c r="C44" s="30">
         <v>1000</v>
       </c>
-      <c r="D44" s="47">
+      <c r="D44" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B45" s="46">
+      <c r="B45" s="45">
         <v>43672</v>
       </c>
       <c r="C45" s="30">
         <v>1818.66</v>
       </c>
-      <c r="D45" s="47">
+      <c r="D45" s="46">
         <v>5</v>
       </c>
     </row>
     <row r="46" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B46" s="46"/>
+      <c r="B46" s="45"/>
       <c r="C46" s="30"/>
-      <c r="D46" s="47"/>
+      <c r="D46" s="46"/>
     </row>
     <row r="47" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B47" s="46">
+      <c r="B47" s="45">
         <v>43616</v>
       </c>
       <c r="C47" s="30">
         <v>1000</v>
       </c>
-      <c r="D47" s="47">
+      <c r="D47" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B48" s="46">
+      <c r="B48" s="45">
         <v>43558</v>
       </c>
       <c r="C48" s="30">
         <v>1731.89</v>
       </c>
-      <c r="D48" s="47">
+      <c r="D48" s="46">
         <v>5</v>
       </c>
     </row>
     <row r="49" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B49" s="46">
+      <c r="B49" s="45">
         <v>43521</v>
       </c>
       <c r="C49" s="30">
         <v>3094.29</v>
       </c>
-      <c r="D49" s="47">
+      <c r="D49" s="46">
         <v>1</v>
       </c>
     </row>

--- a/Asgari-ucret.xlsx
+++ b/Asgari-ucret.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69301463-0096-4E97-923D-6CCFFE00022B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CC96A8-7A2A-4975-9FAB-A8795270CF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="112">
   <si>
     <t>asgari</t>
   </si>
@@ -367,6 +367,12 @@
   </si>
   <si>
     <t>01.01.2019-30.06.2019</t>
+  </si>
+  <si>
+    <t>01.01.2020-30.06.2020</t>
+  </si>
+  <si>
+    <t>01.01.2021-30.06.2021</t>
   </si>
 </sst>
 </file>
@@ -491,9 +497,6 @@
   </cellStyleXfs>
   <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -566,6 +569,9 @@
     <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -955,45 +961,45 @@
     <col min="1" max="1" width="5.140625" customWidth="1"/>
     <col min="2" max="2" width="6.140625" customWidth="1"/>
     <col min="3" max="3" width="6.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7" style="3" customWidth="1"/>
-    <col min="6" max="6" width="6.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="4.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.5703125" style="1" customWidth="1"/>
     <col min="8" max="8" width="5.140625" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" style="3" customWidth="1"/>
     <col min="10" max="10" width="8.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" style="3" customWidth="1"/>
     <col min="12" max="12" width="7.28515625" customWidth="1"/>
-    <col min="13" max="13" width="4.5703125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="4.5703125" style="3" customWidth="1"/>
     <col min="14" max="14" width="5.140625" customWidth="1"/>
-    <col min="15" max="15" width="5.7109375" style="4" customWidth="1"/>
+    <col min="15" max="15" width="5.7109375" style="3" customWidth="1"/>
     <col min="16" max="16" width="6.42578125" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" style="4" customWidth="1"/>
+    <col min="17" max="17" width="5.7109375" style="3" customWidth="1"/>
     <col min="18" max="18" width="5" customWidth="1"/>
-    <col min="19" max="19" width="5.7109375" style="4" customWidth="1"/>
+    <col min="19" max="19" width="5.7109375" style="3" customWidth="1"/>
     <col min="20" max="20" width="6.28515625" customWidth="1"/>
-    <col min="21" max="21" width="4.5703125" style="4" customWidth="1"/>
+    <col min="21" max="21" width="4.5703125" style="3" customWidth="1"/>
     <col min="22" max="22" width="6.28515625" customWidth="1"/>
-    <col min="23" max="23" width="5.7109375" style="4" customWidth="1"/>
+    <col min="23" max="23" width="5.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H2" t="s">
@@ -1022,44 +1028,44 @@
       <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="P3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="R3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="T3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="U3" s="17"/>
-      <c r="V3" s="16" t="s">
+      <c r="U3" s="16"/>
+      <c r="V3" s="15" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1067,217 +1073,217 @@
       <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="6" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C5" s="5"/>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="6" t="s">
+      <c r="E5" s="6"/>
+      <c r="F5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:24" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+      <c r="G5" s="5"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:24" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
         <v>2024</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="17">
         <v>17</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="17">
         <f>$B$6*D6</f>
         <v>612</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>36</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <f>$B$6*F6</f>
         <v>408</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="19">
         <v>24</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <f>D6/F6</f>
         <v>1.5</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="17">
         <f>$B$6*I6</f>
         <v>204</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="20">
         <v>12</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="17">
         <f>$B$6*K6</f>
         <v>204</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="21">
         <v>12</v>
       </c>
-      <c r="L6" s="18">
+      <c r="L6" s="17">
         <f>$B$6*M6</f>
         <v>136</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="22">
         <v>8</v>
       </c>
-      <c r="N6" s="18">
+      <c r="N6" s="17">
         <f>$B$6*O6</f>
         <v>272</v>
       </c>
-      <c r="O6" s="24">
+      <c r="O6" s="23">
         <v>16</v>
       </c>
-      <c r="P6" s="18">
+      <c r="P6" s="17">
         <f>$B$6*Q6</f>
         <v>408</v>
       </c>
-      <c r="Q6" s="25">
+      <c r="Q6" s="24">
         <v>24</v>
       </c>
-      <c r="R6" s="18">
+      <c r="R6" s="17">
         <f>$B$6*S6</f>
         <v>204</v>
       </c>
-      <c r="S6" s="26">
+      <c r="S6" s="25">
         <v>12</v>
       </c>
-      <c r="T6" s="18">
+      <c r="T6" s="17">
         <f>$B$6*U6</f>
         <v>204</v>
       </c>
-      <c r="U6" s="26">
+      <c r="U6" s="25">
         <f>S6</f>
         <v>12</v>
       </c>
-      <c r="V6" s="18">
+      <c r="V6" s="17">
         <f>$B$6*W6</f>
         <v>204</v>
       </c>
-      <c r="W6" s="26">
+      <c r="W6" s="25">
         <f>S6</f>
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B7" s="27"/>
-      <c r="C7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="3"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="2"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2023</v>
       </c>
-      <c r="B8" s="27">
-        <f>Sayfa1!E10/1000</f>
+      <c r="B8" s="26">
+        <f>Sayfa1!E13/1000</f>
         <v>11.40232</v>
       </c>
       <c r="C8">
         <v>240</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <f t="shared" ref="D8:D15" si="0">C8/B8</f>
         <v>21.048348055483448</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>154</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <f t="shared" ref="F8:F15" si="1">E8/B8</f>
         <v>13.506023335601878</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <f t="shared" ref="G8:G15" si="2">D8/F8</f>
         <v>1.5584415584415585</v>
       </c>
       <c r="H8">
         <v>33.6</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="1">
         <f>H8/B8</f>
         <v>2.9467687277676826</v>
       </c>
       <c r="J8">
         <v>78</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <f>J8/B8</f>
         <v>6.8407131180321201</v>
       </c>
       <c r="L8">
         <v>84</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="1">
         <f>L8/B8</f>
         <v>7.3669218194192059</v>
       </c>
       <c r="N8">
         <v>183</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8" s="1">
         <f>N8/B8</f>
         <v>16.049365392306129</v>
       </c>
       <c r="P8">
         <v>225</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <f>P8/B8</f>
         <v>19.732826302015731</v>
       </c>
       <c r="R8">
         <v>96</v>
       </c>
-      <c r="S8" s="2">
+      <c r="S8" s="1">
         <f>R8/B8</f>
         <v>8.4193392221933792</v>
       </c>
       <c r="T8">
         <v>83.16</v>
       </c>
-      <c r="U8" s="2">
+      <c r="U8" s="1">
         <f>T8/B8</f>
         <v>7.2932526012250136</v>
       </c>
       <c r="V8">
         <v>96</v>
       </c>
-      <c r="W8" s="2">
+      <c r="W8" s="1">
         <f t="shared" ref="W8:W13" si="3">V8/B8</f>
         <v>8.4193392221933792</v>
       </c>
@@ -1286,82 +1292,82 @@
       <c r="A9">
         <v>2022</v>
       </c>
-      <c r="B9" s="27">
-        <f>Sayfa1!E12/1000</f>
+      <c r="B9" s="26">
+        <f>Sayfa1!E15/1000</f>
         <v>5.5003500000000001</v>
       </c>
       <c r="C9">
         <v>95</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <f t="shared" si="0"/>
         <v>17.271628169116511</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <f>60032/1000</f>
         <v>60.031999999999996</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <f t="shared" si="1"/>
         <v>10.914214549983182</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <f t="shared" si="2"/>
         <v>1.5824893390191899</v>
       </c>
       <c r="H9">
         <v>19.8</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="1">
         <f>H9/B9</f>
         <v>3.599770923668494</v>
       </c>
       <c r="J9">
         <v>60</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="1">
         <f>J9/B9</f>
         <v>10.908396738389374</v>
       </c>
       <c r="L9">
         <v>42</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="1">
         <f>L9/B9</f>
         <v>7.6358777168725629</v>
       </c>
       <c r="N9">
         <v>84</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9" s="1">
         <f>N9/B9</f>
         <v>15.271755433745126</v>
       </c>
       <c r="P9">
         <v>82</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <f>P9/B9</f>
         <v>14.908142209132146</v>
       </c>
       <c r="R9">
         <v>45</v>
       </c>
-      <c r="S9" s="2">
+      <c r="S9" s="1">
         <f>R9/B9</f>
         <v>8.1812975537920316</v>
       </c>
       <c r="T9">
         <v>48</v>
       </c>
-      <c r="U9" s="2">
+      <c r="U9" s="1">
         <f>T9/B9</f>
         <v>8.7267173907114994</v>
       </c>
       <c r="V9">
         <v>48</v>
       </c>
-      <c r="W9" s="2">
+      <c r="W9" s="1">
         <f t="shared" si="3"/>
         <v>8.7267173907114994</v>
       </c>
@@ -1370,73 +1376,73 @@
       <c r="A10">
         <v>2021</v>
       </c>
-      <c r="B10" s="27">
-        <f>Sayfa1!E14/1000</f>
+      <c r="B10" s="26">
+        <f>Sayfa1!E17/1000</f>
         <v>2.8259000000000003</v>
       </c>
       <c r="C10">
         <v>52</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <f t="shared" si="0"/>
         <v>18.401217311299053</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <f>34092/1000</f>
         <v>34.091999999999999</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <f t="shared" si="1"/>
         <v>12.064121164938602</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <f t="shared" si="2"/>
         <v>1.5252845242285582</v>
       </c>
       <c r="H10">
         <v>12</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="1">
         <f>H10/B10</f>
         <v>4.2464347641459357</v>
       </c>
       <c r="J10">
         <v>30</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="1">
         <f>J10/B10</f>
         <v>10.616086910364839</v>
       </c>
       <c r="L10">
         <v>24</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="1">
         <f>L10/B10</f>
         <v>8.4928695282918714</v>
       </c>
       <c r="N10">
         <v>28.8</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" s="1">
         <f>N10/B10</f>
         <v>10.191443433950246</v>
       </c>
       <c r="P10">
         <v>55.16</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <f>P10/B10</f>
         <v>19.519445132524147</v>
       </c>
       <c r="R10">
         <v>30</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="1">
         <f>R10/B10</f>
         <v>10.616086910364839</v>
       </c>
-      <c r="U10" s="2"/>
-      <c r="W10" s="2">
+      <c r="U10" s="1"/>
+      <c r="W10" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1445,64 +1451,64 @@
       <c r="A11">
         <v>2020</v>
       </c>
-      <c r="B11" s="27">
-        <f>Sayfa1!E16/1000</f>
+      <c r="B11" s="26">
+        <f>Sayfa1!E19/1000</f>
         <v>2.3247100000000001</v>
       </c>
       <c r="C11">
         <v>44</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <f t="shared" si="0"/>
         <v>18.927091981365418</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <f>30558/1000</f>
         <v>30.558</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <f t="shared" si="1"/>
         <v>13.144865381058283</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <f t="shared" si="2"/>
         <v>1.4398848092152627</v>
       </c>
       <c r="H11">
         <v>9.6999999999999993</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="1">
         <f>H11/B11</f>
         <v>4.172563459528285</v>
       </c>
       <c r="J11">
         <v>25</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="1">
         <f>J11/B11</f>
         <v>10.754029534866714</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="1">
         <f>L11/B11</f>
         <v>0</v>
       </c>
       <c r="N11">
         <v>36</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="1">
         <f>N11/B11</f>
         <v>15.485802530208069</v>
       </c>
       <c r="P11">
         <v>35</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <f>P11/B11</f>
         <v>15.055641348813401</v>
       </c>
-      <c r="S11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="W11" s="2">
+      <c r="S11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="W11" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1511,40 +1517,40 @@
       <c r="A12">
         <v>2019</v>
       </c>
-      <c r="B12" s="27">
-        <f>Sayfa1!E18/1000</f>
+      <c r="B12" s="26">
+        <f>Sayfa1!E21/1000</f>
         <v>2.0209000000000001</v>
       </c>
       <c r="C12">
         <v>39</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <f t="shared" si="0"/>
         <v>19.298332426146764</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <f>26400/1000</f>
         <v>26.4</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <f t="shared" si="1"/>
         <v>13.063486565391656</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <f t="shared" si="2"/>
         <v>1.4772727272727273</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="U12" s="2"/>
+      <c r="I12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="U12" s="1"/>
       <c r="V12">
         <v>30.65</v>
       </c>
-      <c r="W12" s="2">
+      <c r="W12" s="1">
         <f t="shared" si="3"/>
         <v>15.166509970805086</v>
       </c>
@@ -1553,40 +1559,40 @@
       <c r="A13">
         <v>2018</v>
       </c>
-      <c r="B13" s="27">
-        <f>Sayfa1!E20/1000</f>
+      <c r="B13" s="26">
+        <f>Sayfa1!E23/1000</f>
         <v>1.6031199999999999</v>
       </c>
       <c r="C13">
         <v>32.5</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <f t="shared" si="0"/>
         <v>20.27296771295973</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f>19686/1000</f>
         <v>19.686</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <f t="shared" si="1"/>
         <v>12.279804381456161</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <f t="shared" si="2"/>
         <v>1.6509194351315657</v>
       </c>
-      <c r="I13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="U13" s="2"/>
+      <c r="I13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="U13" s="1"/>
       <c r="V13">
         <v>25</v>
       </c>
-      <c r="W13" s="2">
+      <c r="W13" s="1">
         <f t="shared" si="3"/>
         <v>15.594590548430562</v>
       </c>
@@ -1595,36 +1601,36 @@
       <c r="A14">
         <v>2017</v>
       </c>
-      <c r="B14" s="27">
-        <f>Sayfa1!E21/1000</f>
+      <c r="B14" s="26">
+        <f>Sayfa1!E24/1000</f>
         <v>1.4040599999999999</v>
       </c>
       <c r="C14">
         <v>27.5</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <f t="shared" si="0"/>
         <v>19.586057575887072</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <f>17050/1000</f>
         <v>17.05</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <f t="shared" si="1"/>
         <v>12.143355697049985</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <f t="shared" si="2"/>
         <v>1.6129032258064515</v>
       </c>
-      <c r="K14" s="28" t="s">
+      <c r="K14" s="27" t="s">
         <v>25</v>
       </c>
       <c r="P14" t="s">
         <v>26</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="Q14" s="3">
         <f>L6+N6+P6+R6+T6+V6</f>
         <v>1428</v>
       </c>
@@ -1633,36 +1639,36 @@
       <c r="A15">
         <v>2016</v>
       </c>
-      <c r="B15" s="27">
-        <f>Sayfa1!E22/1000</f>
+      <c r="B15" s="26">
+        <f>Sayfa1!E25/1000</f>
         <v>1.3009900000000001</v>
       </c>
       <c r="C15">
         <v>25</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <f t="shared" si="0"/>
         <v>19.216135404576512</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f>15125/1000</f>
         <v>15.125</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <f t="shared" si="1"/>
         <v>11.62576191976879</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="1">
         <f t="shared" si="2"/>
         <v>1.6528925619834711</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="J15">
         <v>1768.44</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="3">
         <f>J15/2</f>
         <v>884.22</v>
       </c>
@@ -1673,7 +1679,7 @@
       <c r="P15" t="s">
         <v>27</v>
       </c>
-      <c r="Q15" s="29">
+      <c r="Q15" s="28">
         <f>C6</f>
         <v>612</v>
       </c>
@@ -1685,30 +1691,30 @@
       <c r="C16">
         <v>22.25</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <f>13750/1000</f>
         <v>13.75</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="J16">
         <v>501</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="3">
         <f>J16</f>
         <v>501</v>
       </c>
       <c r="L16">
         <v>410</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="M16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P16" t="s">
         <v>28</v>
       </c>
-      <c r="Q16" s="29">
+      <c r="Q16" s="28">
         <f>+E6</f>
         <v>408</v>
       </c>
@@ -1720,25 +1726,25 @@
       <c r="C17">
         <v>20.5</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <v>12.5</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="2">
         <f>J15/J16</f>
         <v>3.5298203592814374</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="1">
         <f>K15/K16</f>
         <v>1.7649101796407187</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="2">
         <f>L15/L16</f>
         <v>2.1566341463414633</v>
       </c>
       <c r="P17" t="s">
         <v>30</v>
       </c>
-      <c r="Q17" s="17">
+      <c r="Q17" s="16">
         <f>+H6+J6</f>
         <v>408</v>
       </c>
@@ -1750,7 +1756,7 @@
       <c r="C18">
         <v>18.7</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>9</v>
       </c>
     </row>
@@ -1761,10 +1767,10 @@
       <c r="C19">
         <v>17</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <v>10</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="Q19" s="3">
         <f>SUM(Q14:Q18)</f>
         <v>2856</v>
       </c>
@@ -1776,7 +1782,7 @@
       <c r="C20">
         <v>14.8</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2">
         <v>9.5</v>
       </c>
     </row>
@@ -1792,764 +1798,805 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A4:AMJ95"/>
+  <dimension ref="A4:AMJ98"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" style="30"/>
-    <col min="2" max="4" width="35.28515625" style="30" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" style="31" customWidth="1"/>
-    <col min="6" max="6" width="21" style="31" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" style="31" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="30"/>
-    <col min="9" max="10" width="15.42578125" style="30" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="30" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" style="30"/>
-    <col min="13" max="13" width="12.28515625" style="30" customWidth="1"/>
-    <col min="14" max="1024" width="8.42578125" style="30"/>
+    <col min="1" max="1" width="8.42578125" style="29"/>
+    <col min="2" max="4" width="35.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" style="30" customWidth="1"/>
+    <col min="6" max="6" width="21" style="30" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" style="30" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="29"/>
+    <col min="9" max="10" width="15.42578125" style="29" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" style="29"/>
+    <col min="13" max="13" width="12.28515625" style="29" customWidth="1"/>
+    <col min="14" max="1024" width="8.42578125" style="29"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="32"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="30">
-        <f>E9/E18</f>
+      <c r="B4" s="31"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="29">
+        <f>E12/E21</f>
         <v>8.4130832797268535</v>
       </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="J4" s="30">
-        <f>J9/J18</f>
-        <v>6.014383130568338</v>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="J4" s="29">
+        <f>J12/J21</f>
+        <v>5.7274311855981876</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B5" s="32"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
     </row>
     <row r="6" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="34" t="s">
+      <c r="D6" s="32"/>
+      <c r="E6" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="30" t="s">
+      <c r="K6" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="30" t="s">
+      <c r="M6" s="29" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="34" t="s">
+      <c r="C7" s="51"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="34" t="s">
+      <c r="F7" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="G7" s="33" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B8" s="32"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="M8" s="30">
-        <f t="shared" ref="M8:M13" si="0">M9+(M9*D9)</f>
-        <v>12707.133110481325</v>
-      </c>
+      <c r="B8" s="31"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B9" s="32">
-        <v>2024</v>
-      </c>
-      <c r="C9" s="33">
-        <v>2024</v>
-      </c>
-      <c r="D9" s="35">
+      <c r="B9" s="31"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B10" s="31"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B11" s="31"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="M11" s="29">
+        <f t="shared" ref="M11:M16" si="0">M12+(M12*D12)</f>
+        <v>13343.777435465283</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B12" s="31"/>
+      <c r="C12" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="34">
         <v>0.49109999999999998</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E12" s="37">
         <v>17002</v>
       </c>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="I9" s="30">
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="I12" s="29">
         <v>0</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J12" s="29">
         <v>10416.25</v>
       </c>
-      <c r="K9" s="36">
-        <f t="shared" ref="K9:K18" si="1">I9-D9</f>
+      <c r="K12" s="35">
+        <f t="shared" ref="K12:K21" si="1">I12-D12</f>
         <v>-0.49109999999999998</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M12" s="29">
         <f t="shared" si="0"/>
-        <v>8521.9858564022034</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B10" s="37" t="s">
+        <v>8948.9487193785008</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B13" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C13" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="35">
-        <f t="shared" ref="D10:D22" si="2">1-(E10/E9)</f>
+      <c r="D13" s="34">
+        <f t="shared" ref="D13:D25" si="2">1-(E13/E12)</f>
         <v>0.32935419362427953</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E13" s="37">
         <v>11402.32</v>
       </c>
-      <c r="F10" s="38">
+      <c r="F13" s="37">
         <v>13414.5</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G13" s="37">
         <v>15762.04</v>
       </c>
-      <c r="I10" s="35">
-        <f t="shared" ref="I10:I14" si="3">(J9/J10)-1</f>
+      <c r="I13" s="34">
+        <f t="shared" ref="I13:I23" si="3">(J12/J13)-1</f>
         <v>0.38883333333333336</v>
       </c>
-      <c r="J10" s="31">
+      <c r="J13" s="30">
         <f>Sayfa3!C15</f>
         <v>7500</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K13" s="35">
         <f t="shared" si="1"/>
         <v>5.947913970905383E-2</v>
       </c>
-      <c r="M10" s="30">
+      <c r="M13" s="29">
         <f t="shared" si="0"/>
-        <v>6410.6209596167309</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B11" s="37" t="s">
+        <v>6731.8016239002263</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B14" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C14" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D14" s="34">
         <f t="shared" si="2"/>
         <v>0.25394130317338937</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E14" s="37">
         <v>8506.7999999999993</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F14" s="37">
         <v>10008</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G14" s="37">
         <v>11759.4</v>
       </c>
-      <c r="I11" s="35">
+      <c r="I14" s="34">
         <f t="shared" si="3"/>
         <v>0.35154616881712686</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J14" s="30">
         <f>Sayfa3!C22</f>
         <v>5549.2</v>
       </c>
-      <c r="K11" s="36">
+      <c r="K14" s="35">
         <f t="shared" si="1"/>
         <v>9.7604865643737493E-2</v>
       </c>
-      <c r="M11" s="30">
+      <c r="M14" s="29">
         <f t="shared" si="0"/>
-        <v>5112.3772248295572</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B12" s="37" t="s">
+        <v>5368.5141456492747</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B15" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C15" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D15" s="34">
         <f t="shared" si="2"/>
         <v>0.35341726618705027</v>
       </c>
-      <c r="E12" s="38">
+      <c r="E15" s="37">
         <v>5500.35</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F15" s="37">
         <v>6471</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G15" s="37">
         <v>7603.43</v>
       </c>
-      <c r="I12" s="35">
+      <c r="I15" s="34">
         <f t="shared" si="3"/>
         <v>0.29066170484940113</v>
       </c>
-      <c r="J12" s="31">
+      <c r="J15" s="30">
         <f>Sayfa3!C25</f>
         <v>4299.5</v>
       </c>
-      <c r="K12" s="36">
+      <c r="K15" s="35">
         <f t="shared" si="1"/>
         <v>-6.2755561337649146E-2</v>
       </c>
-      <c r="M12" s="30">
+      <c r="M15" s="29">
         <f t="shared" si="0"/>
-        <v>3777.3843681132676</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B13" s="37" t="s">
+        <v>3966.6363654232518</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B16" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C16" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D16" s="34">
         <f t="shared" si="2"/>
         <v>0.22670375521557729</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E16" s="37">
         <v>4253.3999999999996</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F16" s="37">
         <v>5004</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G16" s="37">
         <v>5879.7</v>
       </c>
-      <c r="I13" s="35">
+      <c r="I16" s="34">
         <f t="shared" si="3"/>
         <v>0.42350109423679894</v>
       </c>
-      <c r="J13" s="31">
+      <c r="J16" s="30">
         <f>Sayfa3!C29</f>
         <v>3020.37</v>
       </c>
-      <c r="K13" s="36">
+      <c r="K16" s="35">
         <f t="shared" si="1"/>
         <v>0.19679733902122165</v>
       </c>
-      <c r="M13" s="30">
+      <c r="M16" s="29">
         <f t="shared" si="0"/>
-        <v>3079.2963272941488</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B14" s="37" t="s">
+        <v>3233.5731822441244</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B17" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C17" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D17" s="34">
         <f t="shared" si="2"/>
         <v>0.33561386185169506</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E17" s="37">
         <v>2825.9</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F17" s="37">
         <v>3577.5</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G17" s="37">
         <v>4203.5600000000004</v>
       </c>
-      <c r="I14" s="35">
+      <c r="I17" s="34">
         <f t="shared" si="3"/>
         <v>0.25469726866756659</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J17" s="30">
         <f>Sayfa3!C31</f>
         <v>2407.25</v>
       </c>
-      <c r="K14" s="36">
+      <c r="K17" s="35">
         <f t="shared" si="1"/>
         <v>-8.0916593184128471E-2</v>
       </c>
-      <c r="M14" s="30">
-        <f>M16+(M16*D16)</f>
-        <v>2305.5288772048325</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="36"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B16" s="37" t="s">
+      <c r="M17" s="29">
+        <f>M19+(M19*D19)</f>
+        <v>2421.0389504052455</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="34"/>
+      <c r="E18" s="37">
+        <v>2825.9</v>
+      </c>
+      <c r="F18" s="37">
+        <v>3577.5</v>
+      </c>
+      <c r="G18" s="37"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="30">
+        <v>2048.25</v>
+      </c>
+      <c r="K18" s="35"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B19" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C19" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="35">
-        <f>1-(E16/E14)</f>
+      <c r="D19" s="34">
+        <f>1-(E19/E17)</f>
         <v>0.17735588662019186</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E19" s="37">
         <v>2324.71</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F19" s="37">
         <v>2943</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G19" s="37">
         <v>3458.03</v>
       </c>
-      <c r="I16" s="35">
-        <f>(J14/J16)-1</f>
-        <v>0.24284932468712572</v>
-      </c>
-      <c r="J16" s="31">
-        <f>Sayfa3!C41</f>
+      <c r="I19" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="30">
+        <v>2048.25</v>
+      </c>
+      <c r="K19" s="35">
+        <f t="shared" si="1"/>
+        <v>-0.17735588662019186</v>
+      </c>
+      <c r="M19" s="29">
+        <f>J21+(J21*D21)</f>
+        <v>2056.3357077657001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="37">
+        <v>2324.71</v>
+      </c>
+      <c r="F20" s="37">
+        <v>2943</v>
+      </c>
+      <c r="G20" s="37"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="30">
         <v>1936.88</v>
       </c>
-      <c r="K16" s="36">
+      <c r="K20" s="35"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B21" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="34">
+        <f>1-(E21/E19)</f>
+        <v>0.13068726851951429</v>
+      </c>
+      <c r="E21" s="37">
+        <v>2020.9</v>
+      </c>
+      <c r="F21" s="37">
+        <v>2558.4</v>
+      </c>
+      <c r="G21" s="37">
+        <v>3006.12</v>
+      </c>
+      <c r="I21" s="34">
+        <f t="shared" si="3"/>
+        <v>6.5003903973255062E-2</v>
+      </c>
+      <c r="J21" s="30">
+        <v>1818.66</v>
+      </c>
+      <c r="K21" s="35">
         <f t="shared" si="1"/>
-        <v>6.5493438066933862E-2</v>
-      </c>
-      <c r="M16" s="30">
-        <f>J18+(J18*D18)</f>
-        <v>1958.2259734762617</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="37" t="s">
+        <v>-6.5683364546259226E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B22" s="36"/>
+      <c r="C22" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="36"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B18" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="35">
-        <f>1-(E18/E16)</f>
-        <v>0.13068726851951429</v>
-      </c>
-      <c r="E18" s="38">
+      <c r="D22" s="34"/>
+      <c r="E22" s="37">
         <v>2020.9</v>
       </c>
-      <c r="F18" s="38">
+      <c r="F22" s="37">
         <v>2558.4</v>
       </c>
-      <c r="G18" s="38">
-        <v>3006.12</v>
-      </c>
-      <c r="I18" s="35">
-        <f>(J16/J18)-1</f>
-        <v>0.11836202068260682</v>
-      </c>
-      <c r="J18" s="31">
-        <f>Sayfa3!C48</f>
+      <c r="G22" s="37"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="30">
         <v>1731.89</v>
       </c>
-      <c r="K18" s="36">
-        <f t="shared" si="1"/>
-        <v>-1.2325247836907471E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="35"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="36"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B20" s="37" t="s">
+      <c r="K22" s="35"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B23" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C23" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="35">
-        <f>1-(E20/E18)</f>
+      <c r="D23" s="34">
+        <f>1-(E23/E21)</f>
         <v>0.20672967489732308</v>
       </c>
-      <c r="E20" s="38">
+      <c r="E23" s="37">
         <v>1603.12</v>
       </c>
-      <c r="F20" s="38">
+      <c r="F23" s="37">
         <v>2029.5</v>
       </c>
-      <c r="G20" s="38">
+      <c r="G23" s="37">
         <v>2384.66</v>
       </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="37" t="s">
+      <c r="I23" s="34"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B24" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C24" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D24" s="34">
         <f t="shared" si="2"/>
         <v>0.12417036778282342</v>
       </c>
-      <c r="E21" s="38">
+      <c r="E24" s="37">
         <v>1404.06</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F24" s="37">
         <v>1777.5</v>
       </c>
-      <c r="G21" s="38">
+      <c r="G24" s="37">
         <v>2088.56</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="37" t="s">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B25" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C25" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D25" s="34">
         <f t="shared" si="2"/>
         <v>7.3408543794424741E-2</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E25" s="37">
         <v>1300.99</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F25" s="37">
         <v>1647</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G25" s="37">
         <v>1935.23</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C23" s="30" t="s">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C26" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F26" s="30">
         <v>1273.5</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C24" s="30" t="s">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C27" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F27" s="30">
         <v>1201.5</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C25" s="30" t="s">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C28" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F28" s="30">
         <v>1134</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C26" s="30" t="s">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C29" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="39"/>
-      <c r="F26" s="31">
+      <c r="E29" s="38"/>
+      <c r="F29" s="30">
         <v>1071</v>
       </c>
-      <c r="J26" s="39"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C27" s="30" t="s">
+      <c r="J29" s="38"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C30" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F30" s="30">
         <v>1021.5</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C28" s="30" t="s">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C31" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F31" s="30">
         <v>978.6</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C29" s="30" t="s">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="C32" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="31">
+      <c r="F32" s="30">
         <v>940.5</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C30" s="30" t="s">
+    <row r="33" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C33" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="F30" s="31">
+      <c r="F33" s="30">
         <v>886.5</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C31" s="30" t="s">
+    <row r="34" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C34" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="F31" s="31">
+      <c r="F34" s="30">
         <v>837</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="C32" s="30" t="s">
+    <row r="35" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C35" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="F32" s="31">
+      <c r="F35" s="30">
         <v>796.5</v>
       </c>
     </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C33" s="30" t="s">
+    <row r="36" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C36" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="F33" s="31">
+      <c r="F36" s="30">
         <v>760.5</v>
       </c>
     </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C34" s="30" t="s">
+    <row r="37" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C37" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="F34" s="31">
+      <c r="F37" s="30">
         <v>729</v>
       </c>
     </row>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C35" s="30" t="s">
+    <row r="38" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C38" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="31">
+      <c r="F38" s="30">
         <v>693</v>
       </c>
     </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C36" s="30" t="s">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C39" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="F36" s="31">
+      <c r="F39" s="30">
         <v>666</v>
       </c>
     </row>
-    <row r="37" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C37" s="30" t="s">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C40" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="31">
+      <c r="F40" s="30">
         <v>638.70000000000005</v>
       </c>
     </row>
-    <row r="38" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C38" s="30" t="s">
+    <row r="41" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C41" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F41" s="30">
         <v>608.4</v>
       </c>
     </row>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C39" s="30" t="s">
+    <row r="42" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C42" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F42" s="30">
         <v>585</v>
       </c>
     </row>
-    <row r="40" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C40" s="30" t="s">
+    <row r="43" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C43" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="F40" s="31">
+      <c r="F43" s="30">
         <v>562.5</v>
       </c>
     </row>
-    <row r="41" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C41" s="30" t="s">
+    <row r="44" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C44" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F44" s="30">
         <v>531</v>
       </c>
     </row>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C42" s="30" t="s">
+    <row r="45" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C45" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F45" s="30">
         <v>488.7</v>
       </c>
     </row>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C43" s="30" t="s">
+    <row r="46" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C46" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="31">
+      <c r="F46" s="30">
         <v>444150000</v>
       </c>
     </row>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C44" s="30" t="s">
+    <row r="47" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C47" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F47" s="30">
         <v>423000000</v>
       </c>
     </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C45" s="30" t="s">
+    <row r="48" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C48" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F48" s="30">
         <v>306000000</v>
       </c>
     </row>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C46" s="30" t="s">
+    <row r="49" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C49" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="F46" s="31">
+      <c r="F49" s="30">
         <v>250875000</v>
       </c>
     </row>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C47" s="30" t="s">
+    <row r="50" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C50" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="31">
+      <c r="F50" s="30">
         <v>222000750</v>
       </c>
     </row>
-    <row r="48" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C48" s="30" t="s">
+    <row r="51" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C51" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="F48" s="31">
+      <c r="F51" s="30">
         <v>167940000</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C49" s="30" t="s">
+    <row r="52" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C52" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="F49" s="31">
+      <c r="F52" s="30">
         <v>146947500</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C50" s="30" t="s">
+    <row r="53" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C53" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F53" s="30">
         <v>139950000</v>
       </c>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C51" s="30" t="s">
+    <row r="54" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C54" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F54" s="30">
         <v>118800000</v>
       </c>
     </row>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C52" s="30" t="s">
+    <row r="55" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C55" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="F52" s="31">
+      <c r="F55" s="30">
         <v>109800000</v>
       </c>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B81" s="30" t="s">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B84" s="29" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B83" s="30" t="s">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B86" s="29" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B85" s="30" t="s">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B88" s="29" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B87" s="30" t="s">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B90" s="29" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B89" s="30" t="s">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B92" s="29" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B91" s="30" t="s">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B94" s="29" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B93" s="30" t="s">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B96" s="29" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B95" s="30" t="s">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B98" s="29" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2569,422 +2616,422 @@
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="27" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="40" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="26" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B1" s="41"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="41"/>
     </row>
     <row r="2" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B2" s="41"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="42"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="3" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="42"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="41"/>
     </row>
     <row r="4" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B4" s="41"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="42"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="41"/>
     </row>
     <row r="5" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B5" s="41"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="42"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="41"/>
     </row>
     <row r="6" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B6" s="41"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="42"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="41"/>
     </row>
     <row r="7" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B7" s="41"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="42"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="41"/>
     </row>
     <row r="8" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B8" s="41"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="42"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="41"/>
     </row>
     <row r="9" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B9" s="41"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="42"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="41"/>
     </row>
     <row r="10" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B10" s="41"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="42"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="41"/>
     </row>
     <row r="11" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B11" s="41">
+      <c r="B11" s="40">
         <v>45318</v>
       </c>
-      <c r="C11" s="31">
-        <v>10000</v>
-      </c>
-      <c r="D11" s="42">
+      <c r="C11" s="30">
+        <v>10416</v>
+      </c>
+      <c r="D11" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B12" s="41"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="42"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="41"/>
     </row>
     <row r="13" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B13" s="41">
+      <c r="B13" s="40">
         <v>45287</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <v>7432.53</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B14" s="41">
+      <c r="B14" s="40">
         <v>45244</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="30">
         <v>5000</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B15" s="41">
+      <c r="B15" s="40">
         <v>45134</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="30">
         <v>7500</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="41">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B16" s="41"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="42"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="41"/>
     </row>
     <row r="17" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B17" s="41">
+      <c r="B17" s="40">
         <v>45099</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="30">
         <v>2000</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B18" s="41">
+      <c r="B18" s="40">
         <v>45034</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="30">
         <v>7500</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="41">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B19" s="41">
+      <c r="B19" s="40">
         <v>45034</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="30">
         <v>2000</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B20" s="41">
+      <c r="B20" s="40">
         <v>45012</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="30">
         <v>5589.34</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B21" s="41">
+      <c r="B21" s="40">
         <v>44974</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="30">
         <v>5570.01</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B22" s="41">
+      <c r="B22" s="40">
         <v>44953</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="30">
         <v>5549.2</v>
       </c>
-      <c r="D22" s="42">
+      <c r="D22" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B23" s="41"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="42"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="41"/>
     </row>
     <row r="24" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B24" s="41">
+      <c r="B24" s="40">
         <v>44861</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="30">
         <v>4293.6499999999996</v>
       </c>
-      <c r="D24" s="42">
+      <c r="D24" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B25" s="41">
+      <c r="B25" s="40">
         <v>44769</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="30">
         <v>4299.5</v>
       </c>
-      <c r="D25" s="42">
+      <c r="D25" s="41">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B26" s="41">
+      <c r="B26" s="40">
         <v>44749</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="30">
         <v>1100</v>
       </c>
-      <c r="D26" s="42">
+      <c r="D26" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B27" s="41"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="42"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="41"/>
     </row>
     <row r="28" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B28" s="41">
+      <c r="B28" s="40">
         <v>44680</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="30">
         <v>1100</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D28" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B29" s="41">
+      <c r="B29" s="40">
         <v>44588</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="30">
         <v>3020.37</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="41">
         <v>6</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B30" s="41"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="42"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="41"/>
     </row>
     <row r="31" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B31" s="41">
+      <c r="B31" s="40">
         <v>44557</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="30">
         <v>2407.25</v>
       </c>
-      <c r="D31" s="42">
+      <c r="D31" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B32" s="41"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="42"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="41"/>
     </row>
     <row r="33" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B33" s="41"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="42"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="41"/>
     </row>
     <row r="34" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B34" s="41"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="42"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="41"/>
     </row>
     <row r="35" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B35" s="41">
+      <c r="B35" s="40">
         <v>44039</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="30">
         <v>2048.25</v>
       </c>
-      <c r="D35" s="42">
+      <c r="D35" s="41">
         <v>6</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B36" s="41">
+      <c r="B36" s="40">
         <v>44039</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="30">
         <v>1000</v>
       </c>
-      <c r="D36" s="42">
+      <c r="D36" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B37" s="41"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="42"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="41"/>
     </row>
     <row r="38" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B38" s="41">
+      <c r="B38" s="40">
         <v>44008</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="30">
         <v>1907.58</v>
       </c>
-      <c r="D38" s="42">
+      <c r="D38" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B39" s="41">
+      <c r="B39" s="40">
         <v>43972</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="30">
         <v>1909.32</v>
       </c>
-      <c r="D39" s="42">
+      <c r="D39" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B40" s="41">
+      <c r="B40" s="40">
         <v>43932</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="30">
         <v>1000</v>
       </c>
-      <c r="D40" s="42">
+      <c r="D40" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B41" s="41">
+      <c r="B41" s="40">
         <v>43857</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="30">
         <v>1936.88</v>
       </c>
-      <c r="D41" s="42">
+      <c r="D41" s="41">
         <v>4</v>
       </c>
     </row>
     <row r="42" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B42" s="41"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="42"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="41"/>
     </row>
     <row r="43" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B43" s="41">
+      <c r="B43" s="40">
         <v>43704</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="30">
         <v>1790.78</v>
       </c>
-      <c r="D43" s="42">
+      <c r="D43" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B44" s="41">
+      <c r="B44" s="40">
         <v>43686</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="30">
         <v>1000</v>
       </c>
-      <c r="D44" s="42">
+      <c r="D44" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B45" s="41">
+      <c r="B45" s="40">
         <v>43672</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="30">
         <v>1818.66</v>
       </c>
-      <c r="D45" s="42">
+      <c r="D45" s="41">
         <v>5</v>
       </c>
     </row>
     <row r="46" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B46" s="41"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="42"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="41"/>
     </row>
     <row r="47" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B47" s="41">
+      <c r="B47" s="40">
         <v>43616</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="30">
         <v>1000</v>
       </c>
-      <c r="D47" s="42">
+      <c r="D47" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B48" s="41">
+      <c r="B48" s="40">
         <v>43558</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="30">
         <v>1731.89</v>
       </c>
-      <c r="D48" s="42">
+      <c r="D48" s="41">
         <v>5</v>
       </c>
     </row>
     <row r="49" spans="2:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="B49" s="41">
+      <c r="B49" s="40">
         <v>43521</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="30">
         <v>3094.29</v>
       </c>
-      <c r="D49" s="42">
+      <c r="D49" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3003,7 +3050,7 @@
     <col min="3" max="3" width="12.85546875" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
     <col min="5" max="6" width="8.5703125" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" style="43" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" style="42" customWidth="1"/>
     <col min="8" max="8" width="8.140625" customWidth="1"/>
     <col min="9" max="9" width="9.5703125" customWidth="1"/>
     <col min="10" max="10" width="4.5703125" customWidth="1"/>
@@ -3033,13 +3080,13 @@
       <c r="C2" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="26">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="H3" t="s">
         <v>101</v>
       </c>
@@ -3051,11 +3098,11 @@
       <c r="D4" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="43" t="s">
+      <c r="F4" s="26"/>
+      <c r="G4" s="42" t="s">
         <v>23</v>
       </c>
       <c r="H4" t="s">
@@ -3063,268 +3110,268 @@
       </c>
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="43">
         <v>12</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <f t="shared" ref="E5:E16" si="0">$D$2*D5</f>
         <v>216</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="43">
+      <c r="F5" s="2"/>
+      <c r="G5" s="42">
         <v>0.25</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <f t="shared" ref="H5:H16" si="1">E5*G5</f>
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="43">
         <v>12</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <f t="shared" si="0"/>
         <v>216</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="43">
+      <c r="F6" s="2"/>
+      <c r="G6" s="42">
         <v>0.25</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="44">
         <v>12</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <f t="shared" si="0"/>
         <v>216</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="43">
+      <c r="F7" s="2"/>
+      <c r="G7" s="42">
         <v>0.10630000000000001</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f t="shared" si="1"/>
         <v>22.960800000000003</v>
       </c>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="45">
         <v>10</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="43">
+      <c r="F8" s="2"/>
+      <c r="G8" s="42">
         <v>1</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="46">
         <v>12</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <f t="shared" si="0"/>
         <v>216</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="43">
+      <c r="F9" s="2"/>
+      <c r="G9" s="42">
         <v>1</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <f t="shared" si="1"/>
         <v>216</v>
       </c>
     </row>
     <row r="10" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="47">
         <v>8</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="43">
+      <c r="F10" s="2"/>
+      <c r="G10" s="42">
         <v>0.76461599999999996</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <f t="shared" si="1"/>
         <v>110.104704</v>
       </c>
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="48">
         <v>16</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <f t="shared" si="0"/>
         <v>288</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="43">
+      <c r="F11" s="2"/>
+      <c r="G11" s="42">
         <f>G10</f>
         <v>0.76461599999999996</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <f t="shared" si="1"/>
         <v>220.209408</v>
       </c>
     </row>
     <row r="12" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="49">
         <v>14</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <f t="shared" si="0"/>
         <v>252</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="43">
+      <c r="F12" s="2"/>
+      <c r="G12" s="42">
         <f>G10</f>
         <v>0.76461599999999996</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <f t="shared" si="1"/>
         <v>192.683232</v>
       </c>
     </row>
     <row r="13" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="50">
+      <c r="D13" s="49">
         <v>12</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f t="shared" si="0"/>
         <v>216</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="43">
+      <c r="F13" s="2"/>
+      <c r="G13" s="42">
         <f>G11</f>
         <v>0.76461599999999996</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <f t="shared" si="1"/>
         <v>165.15705599999998</v>
       </c>
     </row>
     <row r="14" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="50">
         <v>12</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <f t="shared" si="0"/>
         <v>216</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="43">
+      <c r="F14" s="2"/>
+      <c r="G14" s="42">
         <f>G13</f>
         <v>0.76461599999999996</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <f t="shared" si="1"/>
         <v>165.15705599999998</v>
       </c>
     </row>
     <row r="15" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="50">
         <v>12</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f t="shared" si="0"/>
         <v>216</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="43">
+      <c r="F15" s="2"/>
+      <c r="G15" s="42">
         <f>G14</f>
         <v>0.76461599999999996</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f t="shared" si="1"/>
         <v>165.15705599999998</v>
       </c>
     </row>
     <row r="16" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="50">
         <f>D14</f>
         <v>12</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <f t="shared" si="0"/>
         <v>216</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="43">
+      <c r="F16" s="2"/>
+      <c r="G16" s="42">
         <f>G15</f>
         <v>0.76461599999999996</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f t="shared" si="1"/>
         <v>165.15705599999998</v>
       </c>
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <f>E16+E15+E14+E13+E11+E10+E9+E8+E7+E5</f>
         <v>2124</v>
       </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="43">
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="42">
         <f>H18/D18</f>
         <v>0.8053608135593221</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <f>SUM(H5:H16)</f>
         <v>1710.5863680000002</v>
       </c>
